--- a/public/templates/teacher_import_template.xlsx
+++ b/public/templates/teacher_import_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Document\WORKING\lavarel_qlgx\public\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B356A7C6-CC69-4503-9C45-5272746722DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38AA8796-68C5-4D4A-9B70-652B2783D877}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
